--- a/sample_data/E_monthly_uploads/2026-09_maadi_report.xlsx
+++ b/sample_data/E_monthly_uploads/2026-09_maadi_report.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J90"/>
+  <dimension ref="A1:K90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,6 +484,11 @@
           <t>تاريخ الصلاحية</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>الشركة</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -522,6 +527,11 @@
       <c r="J5" s="1" t="n">
         <v>46363</v>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -560,6 +570,11 @@
       <c r="J6" s="1" t="n">
         <v>47201</v>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -598,6 +613,11 @@
       <c r="J7" s="1" t="n">
         <v>46623</v>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -638,6 +658,11 @@
           <t>05/2028</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -678,6 +703,11 @@
           <t>16-07-2028</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -718,6 +748,11 @@
       <c r="J10" s="1" t="n">
         <v>46777</v>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -758,6 +793,11 @@
       <c r="J11" s="1" t="n">
         <v>47182</v>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -798,6 +838,11 @@
           <t>02/2028</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -838,6 +883,11 @@
       <c r="J13" s="1" t="n">
         <v>46310</v>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -878,6 +928,11 @@
           <t>27-08-2028</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -916,6 +971,11 @@
       <c r="J15" s="1" t="n">
         <v>46721</v>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -958,6 +1018,11 @@
           <t>01/2029</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -993,6 +1058,11 @@
       <c r="I17" t="n">
         <v>99.45999999999999</v>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1033,6 +1103,11 @@
       <c r="J18" s="1" t="n">
         <v>46871</v>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1073,6 +1148,11 @@
           <t>13-02-2029</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1113,6 +1193,11 @@
           <t>11/2028</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1151,6 +1236,11 @@
       <c r="J21" s="1" t="n">
         <v>46882</v>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1193,6 +1283,11 @@
       <c r="J22" s="1" t="n">
         <v>46934</v>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1231,6 +1326,11 @@
       <c r="J23" s="1" t="n">
         <v>46816</v>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1271,6 +1371,11 @@
           <t>01/2029</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1308,6 +1413,11 @@
       <c r="I25" t="n">
         <v>56.76</v>
       </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1346,6 +1456,11 @@
       <c r="J26" s="1" t="n">
         <v>46929</v>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1384,6 +1499,11 @@
       <c r="J27" s="1" t="n">
         <v>46532</v>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1426,6 +1546,11 @@
           <t>03/2029</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1466,6 +1591,11 @@
           <t>15-10-2026</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1504,6 +1634,11 @@
       <c r="J30" s="1" t="n">
         <v>46978</v>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1541,6 +1676,11 @@
           <t>182.71 جنيه</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1583,6 +1723,11 @@
           <t>07/2027</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1621,6 +1766,11 @@
       <c r="J33" s="1" t="n">
         <v>47112</v>
       </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1663,6 +1813,11 @@
           <t>29-08-2028</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1701,6 +1856,11 @@
       <c r="J35" s="1" t="n">
         <v>47058</v>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1741,6 +1901,11 @@
           <t>08/2028</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1779,6 +1944,11 @@
       <c r="J37" s="1" t="n">
         <v>46303</v>
       </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1814,6 +1984,11 @@
       <c r="I38" t="n">
         <v>52.39</v>
       </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1856,6 +2031,11 @@
           <t>27-04-2028</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1900,6 +2080,11 @@
           <t>01/2028</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1938,6 +2123,11 @@
       <c r="J41" s="1" t="n">
         <v>46807</v>
       </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1976,6 +2166,11 @@
       <c r="J42" s="1" t="n">
         <v>46894</v>
       </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2014,6 +2209,11 @@
       <c r="J43" s="1" t="n">
         <v>47195</v>
       </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2054,6 +2254,11 @@
           <t>10/2028</t>
         </is>
       </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2104,6 +2309,11 @@
       <c r="J46" t="inlineStr">
         <is>
           <t>تاريخ الصلاحية</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>الشركة</t>
         </is>
       </c>
     </row>
@@ -2144,6 +2354,11 @@
       <c r="J47" s="1" t="n">
         <v>47043</v>
       </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2186,6 +2401,11 @@
       <c r="J48" s="1" t="n">
         <v>47127</v>
       </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2224,6 +2444,11 @@
       <c r="J49" s="1" t="n">
         <v>46373</v>
       </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2264,6 +2489,11 @@
           <t>04/2028</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2306,6 +2536,11 @@
           <t>11-01-2027</t>
         </is>
       </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2344,6 +2579,11 @@
       <c r="J52" s="1" t="n">
         <v>46841</v>
       </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2382,6 +2622,11 @@
       <c r="J53" s="1" t="n">
         <v>47079</v>
       </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2424,6 +2669,11 @@
           <t>06/2027</t>
         </is>
       </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2464,6 +2714,11 @@
       <c r="J55" s="1" t="n">
         <v>46832</v>
       </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2504,6 +2759,11 @@
           <t>27-11-2027</t>
         </is>
       </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2542,6 +2802,11 @@
       <c r="J57" s="1" t="n">
         <v>47073</v>
       </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2582,6 +2847,11 @@
           <t>12/2026</t>
         </is>
       </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2620,6 +2890,11 @@
       <c r="J59" s="1" t="n">
         <v>46302</v>
       </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -2662,6 +2937,11 @@
       <c r="J60" s="1" t="n">
         <v>46809</v>
       </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2702,6 +2982,11 @@
           <t>20-10-2026</t>
         </is>
       </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2744,6 +3029,11 @@
           <t>10/2027</t>
         </is>
       </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Beauty Hub</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -2782,6 +3072,11 @@
       <c r="J63" s="1" t="n">
         <v>46754</v>
       </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Beauty Hub</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -2820,6 +3115,11 @@
       <c r="J64" s="1" t="n">
         <v>46661</v>
       </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Beauty Hub</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -2858,6 +3158,11 @@
       <c r="J65" s="1" t="n">
         <v>46853</v>
       </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Beauty Hub</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -2900,6 +3205,11 @@
           <t>07/2027</t>
         </is>
       </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -2938,6 +3248,11 @@
       <c r="J67" s="1" t="n">
         <v>46657</v>
       </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -2976,6 +3291,11 @@
       <c r="J68" s="1" t="n">
         <v>46297</v>
       </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Mother &amp; Baby Co</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -3018,6 +3338,11 @@
       <c r="J69" s="1" t="n">
         <v>47168</v>
       </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Mother &amp; Baby Co</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -3058,6 +3383,11 @@
           <t>11/2026</t>
         </is>
       </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Mother &amp; Baby Co</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -3098,6 +3428,11 @@
           <t>12-06-2028</t>
         </is>
       </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Mother &amp; Baby Co</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -3138,6 +3473,11 @@
       <c r="J72" s="1" t="n">
         <v>46631</v>
       </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -3176,6 +3516,11 @@
       <c r="J73" s="1" t="n">
         <v>46628</v>
       </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -3216,6 +3561,11 @@
           <t>06/2027</t>
         </is>
       </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -3254,6 +3604,11 @@
       <c r="J75" s="1" t="n">
         <v>46565</v>
       </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -3296,6 +3651,11 @@
           <t>02-09-2027</t>
         </is>
       </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -3334,6 +3694,11 @@
       <c r="J77" s="1" t="n">
         <v>46954</v>
       </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -3378,6 +3743,11 @@
           <t>10/2028</t>
         </is>
       </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -3416,6 +3786,11 @@
       <c r="J79" s="1" t="n">
         <v>46613</v>
       </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -3454,6 +3829,11 @@
       <c r="J80" s="1" t="n">
         <v>46846</v>
       </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -3494,6 +3874,11 @@
           <t>10-04-2029</t>
         </is>
       </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -3534,6 +3919,11 @@
           <t>06/2028</t>
         </is>
       </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -3574,6 +3964,11 @@
       <c r="J83" s="1" t="n">
         <v>47169</v>
       </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>MedTech Supplies</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -3614,6 +4009,11 @@
       <c r="J84" s="1" t="n">
         <v>47172</v>
       </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>MedTech Supplies</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -3652,6 +4052,11 @@
       <c r="J85" s="1" t="n">
         <v>47041</v>
       </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>MedTech Supplies</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -3690,6 +4095,11 @@
       <c r="J86" t="inlineStr">
         <is>
           <t>11/2028</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>MedTech Supplies</t>
         </is>
       </c>
     </row>
